--- a/assets/list/graves_missing_photos.xlsx
+++ b/assets/list/graves_missing_photos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1126,13 +1126,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>James Murphy</t>
+          <t>Michael Buckley</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1145,17 +1149,13 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Michael Buckley</t>
+          <t>Cornelius Coleman</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1163,18 +1163,18 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>133</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cornelius Coleman</t>
+          <t>Ellen Noonan</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1182,18 +1182,18 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ellen Noonan</t>
+          <t>Bartholomew Linehan</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1201,18 +1201,18 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>140</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>David Barry</t>
+          <t>David Gilsean</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1220,18 +1220,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Bartholomew Linehan</t>
+          <t>Michael Barry</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1247,10 +1251,14 @@
           <t>140</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>David Gilsean</t>
+          <t>Patrick Hegarty</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1268,12 +1276,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>d</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Michael Barry</t>
+          <t>May Clossey (nee Russell); Christopher Clossey; Ellen (Lena) Clossey</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1291,12 +1299,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>e</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Patrick Hegarty</t>
+          <t>Unknown Unknown</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1314,12 +1322,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>May Clossey (nee Russell); Christopher Clossey; Ellen (Lena) Clossey</t>
+          <t>Elizabeth Collins</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1337,12 +1345,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>g</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Unknown Unknown</t>
+          <t>Hanora Collins; Mary Collins</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1350,22 +1358,18 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Elizabeth Collins</t>
+          <t>Thomas Coughlan</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1373,22 +1377,18 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Hanora Collins; Mary Collins</t>
+          <t>Cornelius Donnell</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1401,13 +1401,13 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>151</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Thomas Coughlan</t>
+          <t>William Twomey; Thomas Twomey; John Twomey</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1415,18 +1415,18 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>143</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cornelius Donnell</t>
+          <t>David Dempsey</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -1434,18 +1434,18 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>144</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>William Twomey; Thomas Twomey; John Twomey</t>
+          <t>Fenaughton</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -1458,13 +1458,13 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>145</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>David Dempsey</t>
+          <t>Mary Fenton</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -1477,13 +1477,13 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>146</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fenaughton</t>
+          <t>John Fenton</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -1496,13 +1496,13 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>147</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mary Fenton</t>
+          <t>John Collins; Hanorah Collins; Mary Collins</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -1515,13 +1515,13 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>148</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>John Fenton</t>
+          <t>Patrick Riordan</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -1534,13 +1534,13 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>149</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>John Collins; Hanorah Collins; Mary Collins</t>
+          <t>Evelyn O'Donoghue</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -1553,13 +1553,13 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>150</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Patrick Riordan</t>
+          <t>Unknown Unknown</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -1572,13 +1572,13 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>152</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Evelyn O'Donoghue</t>
+          <t>Mary O'Neill</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>153</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1610,13 +1610,13 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>154</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mary O'Neill</t>
+          <t>Unknown Unknown</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>155</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>156</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>157</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1700,18 +1700,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Unknown Unknown</t>
+          <t>Orla Kidney</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -1719,101 +1723,21 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>169</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Unknown Unknown</t>
+          <t>Owen McAuliffe</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Thomas Collins; Thomas Collins</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Margaret Mulcahy</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Orla Kidney</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Owen McAuliffe</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/list/graves_missing_photos.xlsx
+++ b/assets/list/graves_missing_photos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -519,10 +519,14 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Denis Linehan; John Linehan; Hannah Linehan; Ellen Linehan; Denis Linehan</t>
+          <t>Patrick (Pad) Mulcahy; Nora (Babs) Mulcahy</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -530,22 +534,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Michael Aherne</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -553,22 +553,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Patrick (Pad) Mulcahy; Nora (Babs) Mulcahy</t>
+          <t>Unknown Unknown</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -576,22 +572,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thomas Manning; Christopher Stanley</t>
+          <t>Unknown Unknown</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -599,18 +591,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Julia Flynn</t>
+          <t>Unknown Unknown</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -618,22 +610,18 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>John Mahony</t>
+          <t>Unknown Unknown</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -641,18 +629,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fitzgerald</t>
+          <t>Unknown Unknown</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -660,22 +648,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>William Mead</t>
+          <t>Unknown Unknown</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -683,18 +667,18 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Michael Aherne</t>
+          <t>Unknown Unknown</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -702,12 +686,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -721,12 +705,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -740,18 +724,18 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Unknown Unknown</t>
+          <t>Marca Carroll; Margaret Carroll</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -759,18 +743,18 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Unknown Unknown</t>
+          <t>John Sheehan; Mary Sheehan</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -778,18 +762,18 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Unknown Unknown</t>
+          <t>Elenora Nagle; Edmond Burke</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -797,18 +781,18 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Unknown Unknown</t>
+          <t>Mary Burke (nee Moore)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -816,37 +800,45 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Unknown Unknown</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>Margaret Conroy</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>k79b.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>170</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Unknown Unknown</t>
+          <t>Coffey</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -854,18 +846,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Unknown Unknown</t>
+          <t>John Cotter</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -873,18 +869,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Marca Carroll; Margaret Carroll</t>
+          <t>Cornelius Clancy</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -892,18 +892,18 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>112</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>John Sheehan; Mary Sheehan</t>
+          <t>Laurence Barry</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -911,18 +911,18 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>113</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Elenora Nagle; Edmond Burke</t>
+          <t>Johanna Meade</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -930,18 +930,18 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>114</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mary Burke (nee Moore)</t>
+          <t>Mary Mullins</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -949,12 +949,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>124</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -964,30 +964,26 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Margaret Conroy</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>k79b.jpg</t>
-        </is>
-      </c>
+          <t>Michael Buckley</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>131</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Coffey</t>
+          <t>Cornelius Coleman</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -995,22 +991,18 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mary Sheridan; Richard Sheridan; Michael Sheridan; Kitty Sheridan; Nellie Sheridan; Ellen Sheridan; Teresa Sheridan</t>
+          <t>Ellen Noonan</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1018,22 +1010,18 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>John Cotter</t>
+          <t>Bartholomew Linehan</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1041,22 +1029,18 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cornelius Clancy</t>
+          <t>David Gilsean</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1064,18 +1048,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Laurence Barry</t>
+          <t>Michael Barry</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1083,18 +1071,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Johanna Meade</t>
+          <t>Patrick Hegarty</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1102,18 +1094,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mary Mullins</t>
+          <t>May Clossey (nee Russell); Christopher Clossey; Ellen (Lena) Clossey</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1121,22 +1117,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>140</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>e</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Michael Buckley</t>
+          <t>Unknown Unknown</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1144,18 +1140,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cornelius Coleman</t>
+          <t>Elizabeth Collins</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1163,18 +1163,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ellen Noonan</t>
+          <t>Hanora Collins; Mary Collins</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1182,18 +1186,18 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>141</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Bartholomew Linehan</t>
+          <t>Thomas Coughlan</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1201,18 +1205,18 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>142</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>David Gilsean</t>
+          <t>Cornelius Donnell</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1220,22 +1224,18 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Michael Barry</t>
+          <t>William Twomey; Thomas Twomey; John Twomey</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1243,22 +1243,18 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Patrick Hegarty</t>
+          <t>David Dempsey</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1266,22 +1262,18 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>May Clossey (nee Russell); Christopher Clossey; Ellen (Lena) Clossey</t>
+          <t>Fenaughton</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1289,22 +1281,18 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Unknown Unknown</t>
+          <t>Mary Fenton</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1312,22 +1300,18 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Elizabeth Collins</t>
+          <t>John Fenton</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1335,22 +1319,18 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Hanora Collins; Mary Collins</t>
+          <t>John Collins; Hanorah Collins; Mary Collins</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1358,18 +1338,18 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>148</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Thomas Coughlan</t>
+          <t>Patrick Riordan</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1377,18 +1357,18 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>149</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cornelius Donnell</t>
+          <t>Evelyn O'Donoghue</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1396,18 +1376,18 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>150</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>William Twomey; Thomas Twomey; John Twomey</t>
+          <t>Unknown Unknown</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1420,13 +1400,13 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>157</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>David Dempsey</t>
+          <t>Unknown Unknown</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -1439,13 +1419,13 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Fenaughton</t>
+          <t>Unknown Unknown</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -1453,18 +1433,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mary Fenton</t>
+          <t>Orla Kidney</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -1472,272 +1456,21 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>169</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>John Fenton</t>
+          <t>Owen McAuliffe</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>John Collins; Hanorah Collins; Mary Collins</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Patrick Riordan</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Evelyn O'Donoghue</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Unknown Unknown</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Mary O'Neill</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Unknown Unknown</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Unknown Unknown</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Unknown Unknown</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Unknown Unknown</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Unknown Unknown</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Unknown Unknown</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Orla Kidney</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Owen McAuliffe</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1750,7 +1483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1793,6 +1526,126 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mary O'Neill</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>t152.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Unknown Unknown</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>t153.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Unknown Unknown</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>t154.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Unknown Unknown</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>t155.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Unknown Unknown</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>t156.jpeg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1804,7 +1657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1918,6 +1771,21 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>e25_e26.jpg</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>filename does not match the {row}{grave}{plot}.ext pattern</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
